--- a/data/output/Garches_Equipe_2_feuille.xlsx
+++ b/data/output/Garches_Equipe_2_feuille.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,779 +425,420 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>geometry/type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>longitude</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>latitude</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>intersection</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ville/Commune</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Code Postale</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Code Département</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Ville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Département</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>equipe</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ordre</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>nb_traversees</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>bande_de_guidage</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>bande_eveil</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>feu_parlant</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>commentaire</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>coordonnees</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t xml:space="preserve">Boulevard   du  Général  de  Gaulle  D907  /  Rue  Frédéric Clément </t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.18863408</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>48.839265104</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Boulevard   du  Général  de  Gaulle  D907  /  Rue  Frédéric Clément </t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H2" t="n">
-        <v>92</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+          <t>48.839265104,2.18863408</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Rue  de  Villeneuve  /  Avenue  de  Lorraine</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.186800801</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>48.840157822</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Rue  de  Villeneuve  /  Avenue  de  Lorraine</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H3" t="n">
-        <v>92</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+          <t>48.840157822,2.186800801</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Avenue  de  Lorraine  /  Avenue  d'Alsace</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.187364881</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>48.842130147</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Avenue  de  Lorraine  /  Avenue  d'Alsace</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H4" t="n">
-        <v>92</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+          <t>48.842130147,2.187364881</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Avenue  d'Alsace  /  Avenue  Foch / Avenue  d'Alsace  /  Jardin  de  la  Mairie / Avenue  d'Alsace  /  Rue  Georges  Clemenceau / Avenue  Foch  /  Avenue   du  Maréchal  Leclerc / Avenue  Foch  /  Jardin  de  la  Mairie / Avenue  Foch  /  Rue  de  l'Abreuvoir / Jardin  de  la  Mairie  /  Avenue  Foch / Rue  Georges  Clemenceau  /  Avenue  Foch</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.186438811</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>48.842677932</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Avenue  d'Alsace  /  Avenue  Foch / Avenue  d'Alsace  /  Jardin  de  la  Mairie / Avenue  d'Alsace  /  Rue  Georges  Clemenceau / Avenue  Foch  /  Avenue   du  Maréchal  Leclerc / Avenue  Foch  /  Jardin  de  la  Mairie / Avenue  Foch  /  Rue  de  l'Abreuvoir / Jardin  de  la  Mairie  /  Avenue  Foch / Rue  Georges  Clemenceau  /  Avenue  Foch</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H5" t="n">
-        <v>92</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+          <t>48.842677932,2.186438811</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.186487926</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>48.842956926</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H6" t="n">
-        <v>92</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+          <t>48.842956926,2.186487926</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.186699047</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>48.843635567</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H7" t="n">
-        <v>92</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+          <t>48.843635567,2.186699047</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Avenue   du  Maréchal  Leclerc  /  Grande  Rue  / Grande  Rue   /  Avenue   du  Maréchal  Leclerc / Rue  Athime  Rué  /  Avenue   du  Maréchal  Leclerc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.186878445</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>48.844591533</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Avenue   du  Maréchal  Leclerc  /  Grande  Rue  / Grande  Rue   /  Avenue   du  Maréchal  Leclerc / Rue  Athime  Rué  /  Avenue   du  Maréchal  Leclerc</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H8" t="n">
-        <v>92</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>7</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+          <t>48.844591533,2.186878445</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Avenue  de  Beauval  /  Place  Charles   Devos</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.186514003</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>48.84484698</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Avenue  de  Beauval  /  Place  Charles   Devos</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H9" t="n">
-        <v>92</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+          <t>48.84484698,2.186514003</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Rue  Athime  Rué  /  Avenue  des  Coteaux</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.185216473</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>48.845861542</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Rue  Athime  Rué  /  Avenue  des  Coteaux</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H10" t="n">
-        <v>92</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>9</v>
-      </c>
-      <c r="M10" t="n">
-        <v>4</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+          <t>48.845861542,2.185216473</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t xml:space="preserve">Avenue  de  Lorraine  /  Grande  Rue </t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.18906415</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>48.844046988</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Avenue  de  Lorraine  /  Grande  Rue </t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H11" t="n">
-        <v>92</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>10</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
+          <t>48.844046988,2.18906415</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Avenue  de  Lorraine  /  Jardin  de  la  Mairie</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.188106937</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>48.843335056</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Avenue  de  Lorraine  /  Jardin  de  la  Mairie</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H12" t="n">
-        <v>92</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
+          <t>48.843335056,2.188106937</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Avenue   du  Parc de  Craon  /  Rue  Henri  Regnault</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Garches, Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.189650758</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>48.847817085</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Avenue   du  Parc de  Craon  /  Rue  Henri  Regnault</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>92033</v>
-      </c>
-      <c r="H13" t="n">
-        <v>92</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Garches</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>12</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+          <t>48.847817085,2.189650758</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/output/Garches_Equipe_2_feuille.xlsx
+++ b/data/output/Garches_Equipe_2_feuille.xlsx
@@ -498,7 +498,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -528,7 +528,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -558,7 +558,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -618,7 +618,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -648,7 +648,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -678,7 +678,7 @@
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -738,7 +738,7 @@
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -768,7 +768,7 @@
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -798,7 +798,7 @@
         <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -828,7 +828,7 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>

--- a/data/output/Garches_Equipe_2_feuille.xlsx
+++ b/data/output/Garches_Equipe_2_feuille.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,56 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>intersection</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ville/Commune</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>equipe</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ordre</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>nb_traversees</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>bande_de_guidage</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>bande_eveil</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>feu_parlant</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>commentaire</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>coordonnees</t>
         </is>
@@ -483,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boulevard   du  Général  de  Gaulle  D907  /  Rue  Frédéric Clément </t>
+          <t>Avenue   du  Maréchal  Leclerc  /  Grande  Rue  / Grande  Rue   /  Avenue   du  Maréchal  Leclerc / Rue  Athime  Rué  /  Avenue   du  Maréchal  Leclerc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,23 +480,20 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>48.839265104,2.18863408</t>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>48.844591533,2.186878445</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rue  de  Villeneuve  /  Avenue  de  Lorraine</t>
+          <t>Avenue  de  Beauval  /  Place  Charles   Devos</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,23 +507,20 @@
       <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>48.840157822,2.186800801</t>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>48.84484698,2.186514003</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Avenue  de  Lorraine  /  Avenue  d'Alsace</t>
+          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,23 +534,20 @@
       <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>48.842130147,2.187364881</t>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>48.843635567,2.186699047</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Avenue  d'Alsace  /  Avenue  Foch / Avenue  d'Alsace  /  Jardin  de  la  Mairie / Avenue  d'Alsace  /  Rue  Georges  Clemenceau / Avenue  Foch  /  Avenue   du  Maréchal  Leclerc / Avenue  Foch  /  Jardin  de  la  Mairie / Avenue  Foch  /  Rue  de  l'Abreuvoir / Jardin  de  la  Mairie  /  Avenue  Foch / Rue  Georges  Clemenceau  /  Avenue  Foch</t>
+          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,23 +561,20 @@
       <c r="D5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>48.842677932,2.186438811</t>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>48.842956926,2.186487926</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
+          <t>Avenue  d'Alsace  /  Avenue  Foch / Avenue  d'Alsace  /  Jardin  de  la  Mairie / Avenue  d'Alsace  /  Rue  Georges  Clemenceau / Avenue  Foch  /  Avenue   du  Maréchal  Leclerc / Avenue  Foch  /  Jardin  de  la  Mairie / Avenue  Foch  /  Rue  de  l'Abreuvoir / Jardin  de  la  Mairie  /  Avenue  Foch / Rue  Georges  Clemenceau  /  Avenue  Foch</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -617,23 +588,20 @@
       <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>48.842956926,2.186487926</t>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>48.842677932,2.186438811</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
+          <t>Avenue  de  Lorraine  /  Avenue  d'Alsace</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -647,23 +615,20 @@
       <c r="D7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>48.843635567,2.186699047</t>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>48.842130147,2.187364881</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Avenue   du  Maréchal  Leclerc  /  Grande  Rue  / Grande  Rue   /  Avenue   du  Maréchal  Leclerc / Rue  Athime  Rué  /  Avenue   du  Maréchal  Leclerc</t>
+          <t>Avenue  de  Lorraine  /  Jardin  de  la  Mairie</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -677,23 +642,20 @@
       <c r="D8" t="n">
         <v>7</v>
       </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>48.844591533,2.186878445</t>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>48.843335056,2.188106937</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Avenue  de  Beauval  /  Place  Charles   Devos</t>
+          <t xml:space="preserve">Avenue  de  Lorraine  /  Grande  Rue </t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -707,16 +669,13 @@
       <c r="D9" t="n">
         <v>8</v>
       </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>48.84484698,2.186514003</t>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>48.844046988,2.18906415</t>
         </is>
       </c>
     </row>
@@ -737,14 +696,11 @@
       <c r="D10" t="n">
         <v>9</v>
       </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>48.845861542,2.185216473</t>
         </is>
@@ -753,7 +709,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avenue  de  Lorraine  /  Grande  Rue </t>
+          <t>Avenue   du  Parc de  Craon  /  Rue  Henri  Regnault</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -767,23 +723,20 @@
       <c r="D11" t="n">
         <v>10</v>
       </c>
-      <c r="E11" t="n">
-        <v>2</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>48.844046988,2.18906415</t>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>48.847817085,2.189650758</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Avenue  de  Lorraine  /  Jardin  de  la  Mairie</t>
+          <t>Rue  de  Villeneuve  /  Avenue  de  Lorraine</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -797,23 +750,20 @@
       <c r="D12" t="n">
         <v>11</v>
       </c>
-      <c r="E12" t="n">
-        <v>3</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>48.843335056,2.188106937</t>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>48.840157822,2.186800801</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Avenue   du  Parc de  Craon  /  Rue  Henri  Regnault</t>
+          <t xml:space="preserve">Boulevard   du  Général  de  Gaulle  D907  /  Rue  Frédéric Clément </t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -827,16 +777,13 @@
       <c r="D13" t="n">
         <v>12</v>
       </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>48.847817085,2.189650758</t>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>48.839265104,2.18863408</t>
         </is>
       </c>
     </row>

--- a/data/output/Garches_Equipe_2_feuille.xlsx
+++ b/data/output/Garches_Equipe_2_feuille.xlsx
@@ -413,25 +413,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>equipe</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>coordonnees</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>intersection</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Ville/Commune</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>equipe</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
           <t>ordre</t>
@@ -439,353 +439,829 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>traversee</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>bande_de_guidage</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>bande_eveil</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>feu_parlant</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>commentaire</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>coordonnees</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Avenue   du  Maréchal  Leclerc  /  Grande  Rue  / Grande  Rue   /  Avenue   du  Maréchal  Leclerc / Rue  Athime  Rué  /  Avenue   du  Maréchal  Leclerc</t>
-        </is>
+      <c r="A2" t="n">
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>2</v>
+          <t>48.839265104,2.18863408</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boulevard   du  Général  de  Gaulle  D907  /  Rue  Frédéric Clément </t>
+        </is>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>48.844591533,2.186878445</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Avenue  de  Beauval  /  Place  Charles   Devos</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
+          <t>48.839265104,2.18863408</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boulevard   du  Général  de  Gaulle  D907  /  Rue  Frédéric Clément </t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>48.84484698,2.186514003</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
-        </is>
+      <c r="A4" t="n">
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
+          <t>48.839265104,2.18863408</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boulevard   du  Général  de  Gaulle  D907  /  Rue  Frédéric Clément </t>
+        </is>
       </c>
       <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>48.843635567,2.186699047</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
-        </is>
+      <c r="A5" t="n">
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
+          <t>48.840157822,2.186800801</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Rue  de  Villeneuve  /  Avenue  de  Lorraine</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>48.842956926,2.186487926</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Avenue  d'Alsace  /  Avenue  Foch / Avenue  d'Alsace  /  Jardin  de  la  Mairie / Avenue  d'Alsace  /  Rue  Georges  Clemenceau / Avenue  Foch  /  Avenue   du  Maréchal  Leclerc / Avenue  Foch  /  Jardin  de  la  Mairie / Avenue  Foch  /  Rue  de  l'Abreuvoir / Jardin  de  la  Mairie  /  Avenue  Foch / Rue  Georges  Clemenceau  /  Avenue  Foch</t>
-        </is>
+      <c r="A6" t="n">
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
+          <t>48.842130147,2.187364881</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Avenue  de  Lorraine  /  Avenue  d'Alsace</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>48.842677932,2.186438811</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>48.842130147,2.187364881</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Avenue  de  Lorraine  /  Avenue  d'Alsace</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
       <c r="D7" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>48.842130147,2.187364881</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Avenue  de  Lorraine  /  Jardin  de  la  Mairie</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avenue  de  Lorraine  /  Avenue  d'Alsace</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>48.843335056,2.188106937</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Avenue  de  Lorraine  /  Grande  Rue </t>
-        </is>
+      <c r="A9" t="n">
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
+          <t>48.842130147,2.187364881</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avenue  de  Lorraine  /  Avenue  d'Alsace</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>48.844046988,2.18906415</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Rue  Athime  Rué  /  Avenue  des  Coteaux</t>
-        </is>
+      <c r="A10" t="n">
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
+          <t>48.842677932,2.186438811</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avenue  d'Alsace  /  Avenue  Foch / Avenue  d'Alsace  /  Jardin  de  la  Mairie / Avenue  d'Alsace  /  Rue  Georges  Clemenceau / Avenue  Foch  /  Avenue   du  Maréchal  Leclerc / Avenue  Foch  /  Jardin  de  la  Mairie / Avenue  Foch  /  Rue  de  l'Abreuvoir / Jardin  de  la  Mairie  /  Avenue  Foch / Rue  Georges  Clemenceau  /  Avenue  Foch</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>48.845861542,2.185216473</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Avenue   du  Parc de  Craon  /  Rue  Henri  Regnault</t>
-        </is>
+      <c r="A11" t="n">
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
+          <t>48.842956926,2.186487926</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>48.847817085,2.189650758</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Rue  de  Villeneuve  /  Avenue  de  Lorraine</t>
-        </is>
+      <c r="A12" t="n">
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
+          <t>48.842956926,2.186487926</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>48.840157822,2.186800801</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Boulevard   du  Général  de  Gaulle  D907  /  Rue  Frédéric Clément </t>
-        </is>
+      <c r="A13" t="n">
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Garches, Hauts-de-Seine</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
+          <t>48.842956926,2.186487926</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>48.839265104,2.18863408</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>48.842956926,2.186487926</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avenue   du  Maréchal  Leclerc  /  Rue  de  l'Abreuvoir / Rue  Claude   Liard  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>48.843635567,2.186699047</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>48.843635567,2.186699047</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>48.843635567,2.186699047</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>48.843635567,2.186699047</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Passage  Albert  Lanoe  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>48.844591533,2.186878445</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avenue   du  Maréchal  Leclerc  /  Grande  Rue  / Grande  Rue   /  Avenue   du  Maréchal  Leclerc / Rue  Athime  Rué  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>48.844591533,2.186878445</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avenue   du  Maréchal  Leclerc  /  Grande  Rue  / Grande  Rue   /  Avenue   du  Maréchal  Leclerc / Rue  Athime  Rué  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>48.844591533,2.186878445</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avenue   du  Maréchal  Leclerc  /  Grande  Rue  / Grande  Rue   /  Avenue   du  Maréchal  Leclerc / Rue  Athime  Rué  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>48.844591533,2.186878445</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Avenue   du  Maréchal  Leclerc  /  Grande  Rue  / Grande  Rue   /  Avenue   du  Maréchal  Leclerc / Rue  Athime  Rué  /  Avenue   du  Maréchal  Leclerc</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>48.84484698,2.186514003</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Avenue  de  Beauval  /  Place  Charles   Devos</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>48.84484698,2.186514003</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Avenue  de  Beauval  /  Place  Charles   Devos</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>48.84484698,2.186514003</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Avenue  de  Beauval  /  Place  Charles   Devos</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>48.845861542,2.185216473</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Rue  Athime  Rué  /  Avenue  des  Coteaux</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>48.845861542,2.185216473</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Rue  Athime  Rué  /  Avenue  des  Coteaux</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>48.844046988,2.18906415</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avenue  de  Lorraine  /  Grande  Rue </t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>48.844046988,2.18906415</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avenue  de  Lorraine  /  Grande  Rue </t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>48.844046988,2.18906415</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avenue  de  Lorraine  /  Grande  Rue </t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>48.844046988,2.18906415</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avenue  de  Lorraine  /  Grande  Rue </t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>48.843335056,2.188106937</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Avenue  de  Lorraine  /  Jardin  de  la  Mairie</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>48.847817085,2.189650758</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Avenue   du  Parc de  Craon  /  Rue  Henri  Regnault</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/output/Garches_Equipe_2_feuille.xlsx
+++ b/data/output/Garches_Equipe_2_feuille.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,12 +469,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.838467608,2.171797485</t>
+          <t>48.839372363,2.171812121</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Allée  de  la  Marc he  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  de  Brétigny  /  Allée  de  la  Marc he</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -503,10 +503,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -544,19 +544,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>48.838040862,2.169032756</t>
+          <t>48.839372363,2.171812121</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boulevard  Raymond  Poincaré  D907  /  Rue  Yves Cariou  D407</t>
+          <t>Avenue  de  Brétigny  /  Allée  de  la  Marc he</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -569,16 +569,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>48.837882396,2.168128382</t>
+          <t>48.838467608,2.171797485</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boulevard  de  la  République  D907  /  Boulevard  Raymond  Poincaré  D907 / Boulevard  Raymond  Poincaré  D907  /  Boulevard  de  la  République  D907</t>
+          <t>Allée  de  la  Marc he  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -594,16 +594,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.837882396,2.168128382</t>
+          <t>48.838467608,2.171797485</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boulevard  de  la  République  D907  /  Boulevard  Raymond  Poincaré  D907 / Boulevard  Raymond  Poincaré  D907  /  Boulevard  de  la  République  D907</t>
+          <t>Allée  de  la  Marc he  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -619,16 +619,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>48.837882396,2.168128382</t>
+          <t>48.838467608,2.171797485</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boulevard  de  la  République  D907  /  Boulevard  Raymond  Poincaré  D907 / Boulevard  Raymond  Poincaré  D907  /  Boulevard  de  la  République  D907</t>
+          <t>Allée  de  la  Marc he  /  Boulevard  Raymond  Poincaré  D907</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
@@ -638,6 +638,156 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>48.838040862,2.169032756</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Boulevard  Raymond  Poincaré  D907  /  Rue  Yves Cariou  D407</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>48.838040862,2.169032756</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Boulevard  Raymond  Poincaré  D907  /  Rue  Yves Cariou  D407</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>48.838040862,2.169032756</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Boulevard  Raymond  Poincaré  D907  /  Rue  Yves Cariou  D407</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>48.838040862,2.169032756</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Boulevard  Raymond  Poincaré  D907  /  Rue  Yves Cariou  D407</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>48.837882396,2.168128382</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Boulevard  de  la  République  D907  /  Boulevard  Raymond  Poincaré  D907 / Boulevard  Raymond  Poincaré  D907  /  Boulevard  de  la  République  D907</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>48.837882396,2.168128382</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Boulevard  de  la  République  D907  /  Boulevard  Raymond  Poincaré  D907 / Boulevard  Raymond  Poincaré  D907  /  Boulevard  de  la  République  D907</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/Garches_Equipe_2_feuille.xlsx
+++ b/data/output/Garches_Equipe_2_feuille.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,12 +469,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.839372363,2.171812121</t>
+          <t>48.806034335,2.318441501</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Allée  de  la  Marc he</t>
+          <t>Avenue  de  Stalingrad  /  Rue  Jean  Marin  Naudin / Rue  Jean  Marin  Naudin  /  Avenue  de  Stalingrad</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -494,12 +494,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>48.839372363,2.171812121</t>
+          <t>48.806034335,2.318441501</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Allée  de  la  Marc he</t>
+          <t>Avenue  de  Stalingrad  /  Rue  Jean  Marin  Naudin / Rue  Jean  Marin  Naudin  /  Avenue  de  Stalingrad</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -519,19 +519,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>48.839372363,2.171812121</t>
+          <t>48.804543053,2.318723747</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Allée  de  la  Marc he</t>
+          <t>Avenue  de  Stalingrad  /  Allée  des  Martyrs  Châteaubriant</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -544,19 +544,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>48.839372363,2.171812121</t>
+          <t>48.804543053,2.318723747</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avenue  de  Brétigny  /  Allée  de  la  Marc he</t>
+          <t>Avenue  de  Stalingrad  /  Allée  des  Martyrs  Châteaubriant</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -569,19 +569,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>48.838467608,2.171797485</t>
+          <t>48.804543053,2.318723747</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Allée  de  la  Marc he  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Avenue  de  Stalingrad  /  Allée  des  Martyrs  Châteaubriant</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -594,19 +594,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.838467608,2.171797485</t>
+          <t>48.803768522,2.320300304</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Allée  de  la  Marc he  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Rue  Gustave  Courbet  /  Avenue  Victor  Hugo  D77a</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -619,19 +619,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>48.838467608,2.171797485</t>
+          <t>48.803768522,2.320300304</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Allée  de  la  Marc he  /  Boulevard  Raymond  Poincaré  D907</t>
+          <t>Rue  Gustave  Courbet  /  Avenue  Victor  Hugo  D77a</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -644,19 +644,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>48.838040862,2.169032756</t>
+          <t>48.803768522,2.320300304</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boulevard  Raymond  Poincaré  D907  /  Rue  Yves Cariou  D407</t>
+          <t>Rue  Gustave  Courbet  /  Avenue  Victor  Hugo  D77a</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -669,19 +669,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>48.838040862,2.169032756</t>
+          <t>48.803768522,2.320300304</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boulevard  Raymond  Poincaré  D907  /  Rue  Yves Cariou  D407</t>
+          <t>Rue  Gustave  Courbet  /  Avenue  Victor  Hugo  D77a</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -694,19 +694,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>48.838040862,2.169032756</t>
+          <t>48.804094776,2.320683591</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boulevard  Raymond  Poincaré  D907  /  Rue  Yves Cariou  D407</t>
+          <t>Avenue  Victor  Hugo  /  Allée  des  Martyrs  Châteaubriant</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -719,19 +719,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>48.838040862,2.169032756</t>
+          <t>48.804094776,2.320683591</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boulevard  Raymond  Poincaré  D907  /  Rue  Yves Cariou  D407</t>
+          <t>Avenue  Victor  Hugo  /  Allée  des  Martyrs  Châteaubriant</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -744,16 +744,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>48.837882396,2.168128382</t>
+          <t>48.803335166,2.319619916</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boulevard  de  la  République  D907  /  Boulevard  Raymond  Poincaré  D907 / Boulevard  Raymond  Poincaré  D907  /  Boulevard  de  la  République  D907</t>
+          <t>Allée  des  Martyrs  Châteaubriant  /  Avenue  Louis  Pasteur / Avenue  Louis  Pasteur  /  Avenue  Henri  Barbusse  D77a / Avenue  Victor  Hugo  D77a  /  Avenue  Louis  Pasteur / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Henri  Barbusse  D77a / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Louis  Pasteur / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Victor  Hugo  D77a</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -769,16 +769,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>48.837882396,2.168128382</t>
+          <t>48.803335166,2.319619916</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boulevard  de  la  République  D907  /  Boulevard  Raymond  Poincaré  D907 / Boulevard  Raymond  Poincaré  D907  /  Boulevard  de  la  République  D907</t>
+          <t>Allée  des  Martyrs  Châteaubriant  /  Avenue  Louis  Pasteur / Avenue  Louis  Pasteur  /  Avenue  Henri  Barbusse  D77a / Avenue  Victor  Hugo  D77a  /  Avenue  Louis  Pasteur / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Henri  Barbusse  D77a / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Louis  Pasteur / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Victor  Hugo  D77a</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -788,6 +788,456 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>48.803335166,2.319619916</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Allée  des  Martyrs  Châteaubriant  /  Avenue  Louis  Pasteur / Avenue  Louis  Pasteur  /  Avenue  Henri  Barbusse  D77a / Avenue  Victor  Hugo  D77a  /  Avenue  Louis  Pasteur / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Henri  Barbusse  D77a / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Louis  Pasteur / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Victor  Hugo  D77a</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>48.803193012,2.318915871</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Allée  des  Martyrs  Châteaubriant  /  Avenue  Henri  Barbusse  D77a</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>48.802872738,2.318221289</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avenue  Henri  Barbusse  D77A  /  Avenue  Henri  Barbusse  D77a</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>48.802872738,2.318221289</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Avenue  Henri  Barbusse  D77A  /  Avenue  Henri  Barbusse  D77a</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>48.802872738,2.318221289</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avenue  Henri  Barbusse  D77A  /  Avenue  Henri  Barbusse  D77a</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>48.802872738,2.318221289</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avenue  Henri  Barbusse  D77A  /  Avenue  Henri  Barbusse  D77a</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>48.802056022,2.318728319</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Rue  de  Verdun  /  Avenue  Louis  Pasteur  D77</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>48.800789452,2.318236971</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Rue  Gabriel  Cosson  /  Avenue  Louis  Pasteur  D77</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>48.800789452,2.318236971</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Rue  Gabriel  Cosson  /  Avenue  Louis  Pasteur  D77</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>48.799722682,2.317922576</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Rue  Jean  Longuet  /  Avenue  Louis  Pasteur  D77</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>48.799722682,2.317922576</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Rue  Jean  Longuet  /  Avenue  Louis  Pasteur  D77</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>48.799722682,2.317922576</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Rue  Jean  Longuet  /  Avenue  Louis  Pasteur  D77</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>48.799722682,2.317922576</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Rue  Jean  Longuet  /  Avenue  Louis  Pasteur  D77</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>48.801212687,2.315028051</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Avenue  Henri  Barbusse  D77A  /  Voie  René  Rousseau / Rue  Gabriel  Cosson  /  Avenue  Henri  Barbusse  D77A</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>48.801212687,2.315028051</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Avenue  Henri  Barbusse  D77A  /  Voie  René  Rousseau / Rue  Gabriel  Cosson  /  Avenue  Henri  Barbusse  D77A</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>48.801212687,2.315028051</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Avenue  Henri  Barbusse  D77A  /  Voie  René  Rousseau / Rue  Gabriel  Cosson  /  Avenue  Henri  Barbusse  D77A</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>48.802006004,2.31651263</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rue  de  Verdun  /  Avenue  Henri  Barbusse  D77A</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>48.802006004,2.31651263</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Rue  de  Verdun  /  Avenue  Henri  Barbusse  D77A</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/Garches_Equipe_2_feuille.xlsx
+++ b/data/output/Garches_Equipe_2_feuille.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,16 +469,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.806034335,2.318441501</t>
+          <t>48.821912505,2.244080972</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avenue  de  Stalingrad  /  Rue  Jean  Marin  Naudin / Rue  Jean  Marin  Naudin  /  Avenue  de  Stalingrad</t>
+          <t>Allée  de  Billa ncourt  /  Avenue   du  Bas-Meudon</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -494,16 +494,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>48.806034335,2.318441501</t>
+          <t>48.821912505,2.244080972</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avenue  de  Stalingrad  /  Rue  Jean  Marin  Naudin / Rue  Jean  Marin  Naudin  /  Avenue  de  Stalingrad</t>
+          <t>Allée  de  Billa ncourt  /  Avenue   du  Bas-Meudon</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -519,19 +519,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>48.804543053,2.318723747</t>
+          <t>48.821912505,2.244080972</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avenue  de  Stalingrad  /  Allée  des  Martyrs  Châteaubriant</t>
+          <t>Allée  de  Billa ncourt  /  Avenue   du  Bas-Meudon</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -544,19 +544,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>48.804543053,2.318723747</t>
+          <t>48.822095553,2.244890221</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avenue  de  Stalingrad  /  Allée  des  Martyrs  Châteaubriant</t>
+          <t>Avenue   du  Bas-Meudon  /  Mail Alfred Boucher</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -569,19 +569,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>48.804543053,2.318723747</t>
+          <t>48.822359641,2.2460078</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avenue  de  Stalingrad  /  Allée  des  Martyrs  Châteaubriant</t>
+          <t>Allée  des  Moulineaux  /  Avenue   du  Bas-Meudon / Avenue   du  Bas-Meudon  /  Allée  Maximilien Luce</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -594,19 +594,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.803768522,2.320300304</t>
+          <t>48.822359641,2.2460078</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rue  Gustave  Courbet  /  Avenue  Victor  Hugo  D77a</t>
+          <t>Allée  des  Moulineaux  /  Avenue   du  Bas-Meudon / Avenue   du  Bas-Meudon  /  Allée  Maximilien Luce</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -619,19 +619,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>48.803768522,2.320300304</t>
+          <t>48.822359641,2.2460078</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rue  Gustave  Courbet  /  Avenue  Victor  Hugo  D77a</t>
+          <t>Allée  des  Moulineaux  /  Avenue   du  Bas-Meudon / Avenue   du  Bas-Meudon  /  Allée  Maximilien Luce</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
         <v>3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -644,19 +644,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>48.803768522,2.320300304</t>
+          <t>48.82270332,2.247440148</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rue  Gustave  Courbet  /  Avenue  Victor  Hugo  D77a</t>
+          <t>Avenue   du  Bas-Meudon  /  Allée  d'Issy</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -669,19 +669,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>48.803768522,2.320300304</t>
+          <t>48.82270332,2.247440148</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rue  Gustave  Courbet  /  Avenue  Victor  Hugo  D77a</t>
+          <t>Avenue   du  Bas-Meudon  /  Allée  d'Issy</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -694,19 +694,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>48.804094776,2.320683591</t>
+          <t>48.82270332,2.247440148</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avenue  Victor  Hugo  /  Allée  des  Martyrs  Châteaubriant</t>
+          <t>Avenue   du  Bas-Meudon  /  Allée  d'Issy</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -719,19 +719,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>48.804094776,2.320683591</t>
+          <t>48.82270332,2.247440148</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avenue  Victor  Hugo  /  Allée  des  Martyrs  Châteaubriant</t>
+          <t>Avenue   du  Bas-Meudon  /  Allée  d'Issy</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
         <v>4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -744,16 +744,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>48.803335166,2.319619916</t>
+          <t>48.822867966,2.248145339</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Allée  des  Martyrs  Châteaubriant  /  Avenue  Louis  Pasteur / Avenue  Louis  Pasteur  /  Avenue  Henri  Barbusse  D77a / Avenue  Victor  Hugo  D77a  /  Avenue  Louis  Pasteur / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Henri  Barbusse  D77a / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Louis  Pasteur / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Victor  Hugo  D77a</t>
+          <t>Allée  des  Pont s  /  Avenue   du  Bas-Meudon / Avenue   du  Bas-Meudon  /  Allée  des  Pont s / Avenue   du  Bas-Meudon  /  Allée  Louis  Bonnier</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -769,16 +769,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>48.803335166,2.319619916</t>
+          <t>48.822867966,2.248145339</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Allée  des  Martyrs  Châteaubriant  /  Avenue  Louis  Pasteur / Avenue  Louis  Pasteur  /  Avenue  Henri  Barbusse  D77a / Avenue  Victor  Hugo  D77a  /  Avenue  Louis  Pasteur / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Henri  Barbusse  D77a / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Louis  Pasteur / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Victor  Hugo  D77a</t>
+          <t>Allée  des  Pont s  /  Avenue   du  Bas-Meudon / Avenue   du  Bas-Meudon  /  Allée  des  Pont s / Avenue   du  Bas-Meudon  /  Allée  Louis  Bonnier</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -794,16 +794,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>48.803335166,2.319619916</t>
+          <t>48.822867966,2.248145339</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Allée  des  Martyrs  Châteaubriant  /  Avenue  Louis  Pasteur / Avenue  Louis  Pasteur  /  Avenue  Henri  Barbusse  D77a / Avenue  Victor  Hugo  D77a  /  Avenue  Louis  Pasteur / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Henri  Barbusse  D77a / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Louis  Pasteur / Rond-Point  des  Martyrs  de  Châteaubriant  /  Avenue  Victor  Hugo  D77a</t>
+          <t>Allée  des  Pont s  /  Avenue   du  Bas-Meudon / Avenue   du  Bas-Meudon  /  Allée  des  Pont s / Avenue   du  Bas-Meudon  /  Allée  Louis  Bonnier</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
         <v>3</v>
@@ -819,19 +819,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>48.803193012,2.318915871</t>
+          <t>48.822867966,2.248145339</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Allée  des  Martyrs  Châteaubriant  /  Avenue  Henri  Barbusse  D77a</t>
+          <t>Allée  des  Pont s  /  Avenue   du  Bas-Meudon / Avenue   du  Bas-Meudon  /  Allée  des  Pont s / Avenue   du  Bas-Meudon  /  Allée  Louis  Bonnier</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -844,12 +844,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>48.802872738,2.318221289</t>
+          <t>48.823132929,2.249309179</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avenue  Henri  Barbusse  D77A  /  Avenue  Henri  Barbusse  D77a</t>
+          <t>Avenue   du  Bas-Meudon  /  Boulevard  des  ÃŽles  D2 / Avenue  Jean  Monnet  /  Boulevard  des  ÃŽles  D2</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -869,12 +869,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>48.802872738,2.318221289</t>
+          <t>48.823132929,2.249309179</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avenue  Henri  Barbusse  D77A  /  Avenue  Henri  Barbusse  D77a</t>
+          <t>Avenue   du  Bas-Meudon  /  Boulevard  des  ÃŽles  D2 / Avenue  Jean  Monnet  /  Boulevard  des  ÃŽles  D2</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -894,12 +894,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>48.802872738,2.318221289</t>
+          <t>48.823132929,2.249309179</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avenue  Henri  Barbusse  D77A  /  Avenue  Henri  Barbusse  D77a</t>
+          <t>Avenue   du  Bas-Meudon  /  Boulevard  des  ÃŽles  D2 / Avenue  Jean  Monnet  /  Boulevard  des  ÃŽles  D2</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -919,12 +919,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>48.802872738,2.318221289</t>
+          <t>48.823132929,2.249309179</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avenue  Henri  Barbusse  D77A  /  Avenue  Henri  Barbusse  D77a</t>
+          <t>Avenue   du  Bas-Meudon  /  Boulevard  des  ÃŽles  D2 / Avenue  Jean  Monnet  /  Boulevard  des  ÃŽles  D2</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -944,19 +944,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>48.802056022,2.318728319</t>
+          <t>48.823132929,2.249309179</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rue  de  Verdun  /  Avenue  Louis  Pasteur  D77</t>
+          <t>Avenue   du  Bas-Meudon  /  Boulevard  des  ÃŽles  D2 / Avenue  Jean  Monnet  /  Boulevard  des  ÃŽles  D2</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -969,19 +969,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>48.800789452,2.318236971</t>
+          <t>48.823132929,2.249309179</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rue  Gabriel  Cosson  /  Avenue  Louis  Pasteur  D77</t>
+          <t>Avenue   du  Bas-Meudon  /  Boulevard  des  ÃŽles  D2 / Avenue  Jean  Monnet  /  Boulevard  des  ÃŽles  D2</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -994,19 +994,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>48.800789452,2.318236971</t>
+          <t>48.823132929,2.249309179</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rue  Gabriel  Cosson  /  Avenue  Louis  Pasteur  D77</t>
+          <t>Avenue   du  Bas-Meudon  /  Boulevard  des  ÃŽles  D2 / Avenue  Jean  Monnet  /  Boulevard  des  ÃŽles  D2</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
@@ -1019,16 +1019,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>48.799722682,2.317922576</t>
+          <t>48.821869748,2.250249377</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rue  Jean  Longuet  /  Avenue  Louis  Pasteur  D77</t>
+          <t>Boulevard  des  ÃŽles  D2  /  Quai de  la  Bataille de  Stalingrad  D7 / Place  de  la  Résistance  /  Boulevard  des  ÃŽles  D2 / Quai de  la  Bataille de  Stalingrad  D7  /  Boulevard  des  ÃŽles  D2</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -1044,16 +1044,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>48.799722682,2.317922576</t>
+          <t>48.821869748,2.250249377</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rue  Jean  Longuet  /  Avenue  Louis  Pasteur  D77</t>
+          <t>Boulevard  des  ÃŽles  D2  /  Quai de  la  Bataille de  Stalingrad  D7 / Place  de  la  Résistance  /  Boulevard  des  ÃŽles  D2 / Quai de  la  Bataille de  Stalingrad  D7  /  Boulevard  des  ÃŽles  D2</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
@@ -1069,16 +1069,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>48.799722682,2.317922576</t>
+          <t>48.821869748,2.250249377</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rue  Jean  Longuet  /  Avenue  Louis  Pasteur  D77</t>
+          <t>Boulevard  des  ÃŽles  D2  /  Quai de  la  Bataille de  Stalingrad  D7 / Place  de  la  Résistance  /  Boulevard  des  ÃŽles  D2 / Quai de  la  Bataille de  Stalingrad  D7  /  Boulevard  des  ÃŽles  D2</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
         <v>3</v>
@@ -1094,16 +1094,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>48.799722682,2.317922576</t>
+          <t>48.821869748,2.250249377</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rue  Jean  Longuet  /  Avenue  Louis  Pasteur  D77</t>
+          <t>Boulevard  des  ÃŽles  D2  /  Quai de  la  Bataille de  Stalingrad  D7 / Place  de  la  Résistance  /  Boulevard  des  ÃŽles  D2 / Quai de  la  Bataille de  Stalingrad  D7  /  Boulevard  des  ÃŽles  D2</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
         <v>4</v>
@@ -1119,19 +1119,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>48.801212687,2.315028051</t>
+          <t>48.821869748,2.250249377</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avenue  Henri  Barbusse  D77A  /  Voie  René  Rousseau / Rue  Gabriel  Cosson  /  Avenue  Henri  Barbusse  D77A</t>
+          <t>Boulevard  des  ÃŽles  D2  /  Quai de  la  Bataille de  Stalingrad  D7 / Place  de  la  Résistance  /  Boulevard  des  ÃŽles  D2 / Quai de  la  Bataille de  Stalingrad  D7  /  Boulevard  des  ÃŽles  D2</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
@@ -1144,19 +1144,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>48.801212687,2.315028051</t>
+          <t>48.821869748,2.250249377</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avenue  Henri  Barbusse  D77A  /  Voie  René  Rousseau / Rue  Gabriel  Cosson  /  Avenue  Henri  Barbusse  D77A</t>
+          <t>Boulevard  des  ÃŽles  D2  /  Quai de  la  Bataille de  Stalingrad  D7 / Place  de  la  Résistance  /  Boulevard  des  ÃŽles  D2 / Quai de  la  Bataille de  Stalingrad  D7  /  Boulevard  des  ÃŽles  D2</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
@@ -1169,19 +1169,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>48.801212687,2.315028051</t>
+          <t>48.818192406,2.247366134</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avenue  Henri  Barbusse  D77A  /  Voie  René  Rousseau / Rue  Gabriel  Cosson  /  Avenue  Henri  Barbusse  D77A</t>
+          <t>Allée  de  la  Ferme  /  Avenue  de  Verdun  D989</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>11</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>48.802006004,2.31651263</t>
+          <t>48.818466626,2.245882939</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rue  de  Verdun  /  Avenue  Henri  Barbusse  D77A</t>
+          <t>Avenue  de  Verdun  D989  /  Place  Tony de  Graaff / Avenue  de  Verdun  /  Rue  de  Meudon / Avenue  de  Verdun  D989  /  Rue   du   Docteur  Vuillième / Rue  de  Meudon  /  Avenue  de  Verdun  D989 / Rue   du   Docteur  Vuillième  /  Avenue  de  Verdun  D989</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>48.802006004,2.31651263</t>
+          <t>48.818466626,2.245882939</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rue  de  Verdun  /  Avenue  Henri  Barbusse  D77A</t>
+          <t>Avenue  de  Verdun  D989  /  Place  Tony de  Graaff / Avenue  de  Verdun  /  Rue  de  Meudon / Avenue  de  Verdun  D989  /  Rue   du   Docteur  Vuillième / Rue  de  Meudon  /  Avenue  de  Verdun  D989 / Rue   du   Docteur  Vuillième  /  Avenue  de  Verdun  D989</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1238,6 +1238,831 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>48.818466626,2.245882939</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Place  Tony de  Graaff / Avenue  de  Verdun  /  Rue  de  Meudon / Avenue  de  Verdun  D989  /  Rue   du   Docteur  Vuillième / Rue  de  Meudon  /  Avenue  de  Verdun  D989 / Rue   du   Docteur  Vuillième  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>48.818466626,2.245882939</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Place  Tony de  Graaff / Avenue  de  Verdun  /  Rue  de  Meudon / Avenue  de  Verdun  D989  /  Rue   du   Docteur  Vuillième / Rue  de  Meudon  /  Avenue  de  Verdun  D989 / Rue   du   Docteur  Vuillième  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>48.818466626,2.245882939</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Place  Tony de  Graaff / Avenue  de  Verdun  /  Rue  de  Meudon / Avenue  de  Verdun  D989  /  Rue   du   Docteur  Vuillième / Rue  de  Meudon  /  Avenue  de  Verdun  D989 / Rue   du   Docteur  Vuillième  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12</v>
+      </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>48.818466626,2.245882939</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Place  Tony de  Graaff / Avenue  de  Verdun  /  Rue  de  Meudon / Avenue  de  Verdun  D989  /  Rue   du   Docteur  Vuillième / Rue  de  Meudon  /  Avenue  de  Verdun  D989 / Rue   du   Docteur  Vuillième  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>48.818466626,2.245882939</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Place  Tony de  Graaff / Avenue  de  Verdun  /  Rue  de  Meudon / Avenue  de  Verdun  D989  /  Rue   du   Docteur  Vuillième / Rue  de  Meudon  /  Avenue  de  Verdun  D989 / Rue   du   Docteur  Vuillième  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12</v>
+      </c>
+      <c r="E37" t="n">
+        <v>7</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>48.818466626,2.245882939</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Place  Tony de  Graaff / Avenue  de  Verdun  /  Rue  de  Meudon / Avenue  de  Verdun  D989  /  Rue   du   Docteur  Vuillième / Rue  de  Meudon  /  Avenue  de  Verdun  D989 / Rue   du   Docteur  Vuillième  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12</v>
+      </c>
+      <c r="E38" t="n">
+        <v>8</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>48.818466626,2.245882939</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Place  Tony de  Graaff / Avenue  de  Verdun  /  Rue  de  Meudon / Avenue  de  Verdun  D989  /  Rue   du   Docteur  Vuillième / Rue  de  Meudon  /  Avenue  de  Verdun  D989 / Rue   du   Docteur  Vuillième  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12</v>
+      </c>
+      <c r="E39" t="n">
+        <v>9</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>48.818610293,2.245169319</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  /  Rue  Gabriel  Thomas</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>13</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>48.818610293,2.245169319</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  /  Rue  Gabriel  Thomas</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>13</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>48.818610293,2.245169319</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  /  Rue  Gabriel  Thomas</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>13</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>48.818890946,2.24370838</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Rue  Marcel  Miquel  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>14</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>48.818890946,2.24370838</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Rue  Marcel  Miquel  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>14</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>48.818890946,2.24370838</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Rue  Marcel  Miquel  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>14</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>48.818890946,2.24370838</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Rue  Marcel  Miquel  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>14</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>48.818890946,2.24370838</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Rue  Marcel  Miquel  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>14</v>
+      </c>
+      <c r="E47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>48.81930032,2.242712451</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Rue  de  Vaugirard  D989  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>15</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>48.81930032,2.242712451</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Rue  de  Vaugirard  D989  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>15</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>48.81930032,2.242712451</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Rue  de  Vaugirard  D989  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>15</v>
+      </c>
+      <c r="E50" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>48.81930032,2.242712451</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Rue  de  Vaugirard  D989  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>15</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>48.817810622,2.249042519</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Carrefour de  la  Ferme / Avenue  de  Verdun  D989  /  Chemin de  Saint-Cloud / Avenue  de  Verdun  D989  /  Rue  de  Paris / Chemin de  Saint-Cloud  /  Avenue  de  Verdun / Rue  Jean-Pierre  Timbaud  D101  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>16</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>48.817810622,2.249042519</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Carrefour de  la  Ferme / Avenue  de  Verdun  D989  /  Chemin de  Saint-Cloud / Avenue  de  Verdun  D989  /  Rue  de  Paris / Chemin de  Saint-Cloud  /  Avenue  de  Verdun / Rue  Jean-Pierre  Timbaud  D101  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>16</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>48.817810622,2.249042519</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Carrefour de  la  Ferme / Avenue  de  Verdun  D989  /  Chemin de  Saint-Cloud / Avenue  de  Verdun  D989  /  Rue  de  Paris / Chemin de  Saint-Cloud  /  Avenue  de  Verdun / Rue  Jean-Pierre  Timbaud  D101  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>16</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>48.817810622,2.249042519</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Carrefour de  la  Ferme / Avenue  de  Verdun  D989  /  Chemin de  Saint-Cloud / Avenue  de  Verdun  D989  /  Rue  de  Paris / Chemin de  Saint-Cloud  /  Avenue  de  Verdun / Rue  Jean-Pierre  Timbaud  D101  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>16</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>48.817810622,2.249042519</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Carrefour de  la  Ferme / Avenue  de  Verdun  D989  /  Chemin de  Saint-Cloud / Avenue  de  Verdun  D989  /  Rue  de  Paris / Chemin de  Saint-Cloud  /  Avenue  de  Verdun / Rue  Jean-Pierre  Timbaud  D101  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>16</v>
+      </c>
+      <c r="E56" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>48.817810622,2.249042519</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Carrefour de  la  Ferme / Avenue  de  Verdun  D989  /  Chemin de  Saint-Cloud / Avenue  de  Verdun  D989  /  Rue  de  Paris / Chemin de  Saint-Cloud  /  Avenue  de  Verdun / Rue  Jean-Pierre  Timbaud  D101  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>16</v>
+      </c>
+      <c r="E57" t="n">
+        <v>6</v>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>48.817810622,2.249042519</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Carrefour de  la  Ferme / Avenue  de  Verdun  D989  /  Chemin de  Saint-Cloud / Avenue  de  Verdun  D989  /  Rue  de  Paris / Chemin de  Saint-Cloud  /  Avenue  de  Verdun / Rue  Jean-Pierre  Timbaud  D101  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>16</v>
+      </c>
+      <c r="E58" t="n">
+        <v>7</v>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>48.81799295,2.250857022</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Allée  de  la  Brasserie  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>17</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>48.818083541,2.251255985</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Chemin des  Montquartiers</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>18</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>48.818083541,2.251255985</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Chemin des  Montquartiers</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>18</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>48.818274966,2.251818331</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Rue   du   Docteur  Lombard  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>19</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>48.818274966,2.251818331</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Rue   du   Docteur  Lombard  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>19</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>48.818958475,2.254043502</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Cours  Saint-Vincent / Chemin des  Vignes  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>21</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>48.818958475,2.254043502</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Avenue  de  Verdun  D989  /  Cours  Saint-Vincent / Chemin des  Vignes  /  Avenue  de  Verdun  D989</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>21</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2</v>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
